--- a/artfynd/A 31635-2024 artfynd.xlsx
+++ b/artfynd/A 31635-2024 artfynd.xlsx
@@ -6288,10 +6288,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119480913</v>
+        <v>119480914</v>
       </c>
       <c r="B57" t="n">
-        <v>91463</v>
+        <v>97907</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6300,25 +6300,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6328,10 +6328,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>799615</v>
+        <v>799784</v>
       </c>
       <c r="R57" t="n">
-        <v>7310828</v>
+        <v>7310596</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6390,10 +6390,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119480914</v>
+        <v>119480913</v>
       </c>
       <c r="B58" t="n">
-        <v>97907</v>
+        <v>91463</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6402,25 +6402,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6430,10 +6430,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>799784</v>
+        <v>799615</v>
       </c>
       <c r="R58" t="n">
-        <v>7310596</v>
+        <v>7310828</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7007,7 +7007,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119480807</v>
+        <v>119483568</v>
       </c>
       <c r="B64" t="n">
         <v>97907</v>
@@ -7043,14 +7043,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösön, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>799805</v>
+        <v>799765</v>
       </c>
       <c r="R64" t="n">
-        <v>7310561</v>
+        <v>7310738</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7097,19 +7097,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119483568</v>
+        <v>119480807</v>
       </c>
       <c r="B65" t="n">
         <v>97907</v>
@@ -7145,14 +7145,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mjösön, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>799765</v>
+        <v>799805</v>
       </c>
       <c r="R65" t="n">
-        <v>7310738</v>
+        <v>7310561</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7199,12 +7199,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8231,10 +8231,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119480783</v>
+        <v>119480785</v>
       </c>
       <c r="B76" t="n">
-        <v>91463</v>
+        <v>97074</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8243,25 +8243,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4745</v>
+        <v>220250</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8271,10 +8271,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>799589</v>
+        <v>799809</v>
       </c>
       <c r="R76" t="n">
-        <v>7310819</v>
+        <v>7310563</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8333,10 +8333,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119480785</v>
+        <v>119480797</v>
       </c>
       <c r="B77" t="n">
-        <v>97074</v>
+        <v>97907</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8345,25 +8345,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220250</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>799809</v>
+        <v>799531</v>
       </c>
       <c r="R77" t="n">
-        <v>7310563</v>
+        <v>7310646</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8435,7 +8435,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119480797</v>
+        <v>119480916</v>
       </c>
       <c r="B78" t="n">
         <v>97907</v>
@@ -8475,10 +8475,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>799531</v>
+        <v>799575</v>
       </c>
       <c r="R78" t="n">
-        <v>7310646</v>
+        <v>7310814</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8525,19 +8525,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119480916</v>
+        <v>119480920</v>
       </c>
       <c r="B79" t="n">
         <v>97907</v>
@@ -8577,10 +8577,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>799575</v>
+        <v>799655</v>
       </c>
       <c r="R79" t="n">
-        <v>7310814</v>
+        <v>7310594</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8639,10 +8639,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119480920</v>
+        <v>119480783</v>
       </c>
       <c r="B80" t="n">
-        <v>97907</v>
+        <v>91463</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8651,25 +8651,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8679,10 +8679,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>799655</v>
+        <v>799589</v>
       </c>
       <c r="R80" t="n">
-        <v>7310594</v>
+        <v>7310819</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8729,12 +8729,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 31635-2024 artfynd.xlsx
+++ b/artfynd/A 31635-2024 artfynd.xlsx
@@ -7007,7 +7007,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119483568</v>
+        <v>119480807</v>
       </c>
       <c r="B64" t="n">
         <v>97907</v>
@@ -7043,14 +7043,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mjösön, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>799765</v>
+        <v>799805</v>
       </c>
       <c r="R64" t="n">
-        <v>7310738</v>
+        <v>7310561</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7097,19 +7097,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119480807</v>
+        <v>119483568</v>
       </c>
       <c r="B65" t="n">
         <v>97907</v>
@@ -7145,14 +7145,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösön, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>799805</v>
+        <v>799765</v>
       </c>
       <c r="R65" t="n">
-        <v>7310561</v>
+        <v>7310738</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7199,12 +7199,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8231,10 +8231,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119480785</v>
+        <v>119480783</v>
       </c>
       <c r="B76" t="n">
-        <v>97074</v>
+        <v>91463</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8243,25 +8243,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220250</v>
+        <v>4745</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8271,10 +8271,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>799809</v>
+        <v>799589</v>
       </c>
       <c r="R76" t="n">
-        <v>7310563</v>
+        <v>7310819</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8333,10 +8333,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119480797</v>
+        <v>119480785</v>
       </c>
       <c r="B77" t="n">
-        <v>97907</v>
+        <v>97074</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8345,25 +8345,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>220250</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>799531</v>
+        <v>799809</v>
       </c>
       <c r="R77" t="n">
-        <v>7310646</v>
+        <v>7310563</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8435,7 +8435,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119480916</v>
+        <v>119480797</v>
       </c>
       <c r="B78" t="n">
         <v>97907</v>
@@ -8475,10 +8475,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>799575</v>
+        <v>799531</v>
       </c>
       <c r="R78" t="n">
-        <v>7310814</v>
+        <v>7310646</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8525,19 +8525,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119480920</v>
+        <v>119480916</v>
       </c>
       <c r="B79" t="n">
         <v>97907</v>
@@ -8577,10 +8577,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>799655</v>
+        <v>799575</v>
       </c>
       <c r="R79" t="n">
-        <v>7310594</v>
+        <v>7310814</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8639,10 +8639,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119480783</v>
+        <v>119480920</v>
       </c>
       <c r="B80" t="n">
-        <v>91463</v>
+        <v>97907</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8651,25 +8651,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8679,10 +8679,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>799589</v>
+        <v>799655</v>
       </c>
       <c r="R80" t="n">
-        <v>7310819</v>
+        <v>7310594</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8729,12 +8729,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 31635-2024 artfynd.xlsx
+++ b/artfynd/A 31635-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10280,6 +10280,127 @@
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>127742523</v>
+      </c>
+      <c r="B96" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Mjösjön bdn, Nb</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>799773</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7310800</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31635-2024 artfynd.xlsx
+++ b/artfynd/A 31635-2024 artfynd.xlsx
@@ -10285,7 +10285,7 @@
         <v>127742523</v>
       </c>
       <c r="B96" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 31635-2024 artfynd.xlsx
+++ b/artfynd/A 31635-2024 artfynd.xlsx
@@ -10285,7 +10285,7 @@
         <v>127742523</v>
       </c>
       <c r="B96" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 31635-2024 artfynd.xlsx
+++ b/artfynd/A 31635-2024 artfynd.xlsx
@@ -10285,7 +10285,7 @@
         <v>127742523</v>
       </c>
       <c r="B96" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 31635-2024 artfynd.xlsx
+++ b/artfynd/A 31635-2024 artfynd.xlsx
@@ -10285,7 +10285,7 @@
         <v>127742523</v>
       </c>
       <c r="B96" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 31635-2024 artfynd.xlsx
+++ b/artfynd/A 31635-2024 artfynd.xlsx
@@ -10285,7 +10285,7 @@
         <v>127742523</v>
       </c>
       <c r="B96" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 31635-2024 artfynd.xlsx
+++ b/artfynd/A 31635-2024 artfynd.xlsx
@@ -10285,7 +10285,7 @@
         <v>127742523</v>
       </c>
       <c r="B96" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 31635-2024 artfynd.xlsx
+++ b/artfynd/A 31635-2024 artfynd.xlsx
@@ -10285,7 +10285,7 @@
         <v>127742523</v>
       </c>
       <c r="B96" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 31635-2024 artfynd.xlsx
+++ b/artfynd/A 31635-2024 artfynd.xlsx
@@ -10285,7 +10285,7 @@
         <v>127742523</v>
       </c>
       <c r="B96" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 31635-2024 artfynd.xlsx
+++ b/artfynd/A 31635-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119354088</v>
+        <v>119354094</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>799512</v>
+        <v>799626</v>
       </c>
       <c r="R2" t="n">
-        <v>7310590</v>
+        <v>7310570</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119354078</v>
+        <v>119480808</v>
       </c>
       <c r="B3" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>799579</v>
+        <v>799610</v>
       </c>
       <c r="R3" t="n">
-        <v>7310601</v>
+        <v>7310908</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,6 +851,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,50 +870,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119354114</v>
+        <v>119480809</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>799710</v>
+        <v>799536</v>
       </c>
       <c r="R4" t="n">
-        <v>7310648</v>
+        <v>7310553</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +935,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,15 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119354103</v>
+        <v>119354101</v>
       </c>
       <c r="B5" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>799670</v>
+        <v>799575</v>
       </c>
       <c r="R5" t="n">
-        <v>7310565</v>
+        <v>7310610</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,37 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119354093</v>
+        <v>119354102</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>799769</v>
+        <v>799623</v>
       </c>
       <c r="R6" t="n">
-        <v>7310556</v>
+        <v>7310571</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1161,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119354090</v>
+        <v>119354103</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>799583</v>
+        <v>799670</v>
       </c>
       <c r="R7" t="n">
-        <v>7310620</v>
+        <v>7310565</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,37 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119354082</v>
+        <v>119354078</v>
       </c>
       <c r="B8" t="n">
-        <v>93935</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2387</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>799543</v>
+        <v>799579</v>
       </c>
       <c r="R8" t="n">
-        <v>7310620</v>
+        <v>7310601</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,50 +1355,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119354113</v>
+        <v>119480813</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>799729</v>
+        <v>799625</v>
       </c>
       <c r="R9" t="n">
-        <v>7310626</v>
+        <v>7310588</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,12 +1420,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1473,6 +1434,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1491,37 +1453,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119354075</v>
+        <v>119354082</v>
       </c>
       <c r="B10" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2387</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1488,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>799612</v>
+        <v>799543</v>
       </c>
       <c r="R10" t="n">
-        <v>7310583</v>
+        <v>7310620</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,50 +1550,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119354072</v>
+        <v>119480788</v>
       </c>
       <c r="B11" t="n">
-        <v>91463</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4745</v>
+        <v>2387</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>799710</v>
+        <v>799531</v>
       </c>
       <c r="R11" t="n">
-        <v>7310658</v>
+        <v>7310654</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,12 +1615,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>kolla upp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,15 +1652,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119354098</v>
+        <v>119480815</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92037</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,34 +1663,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>3277</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>799583</v>
+        <v>799561</v>
       </c>
       <c r="R12" t="n">
-        <v>7310614</v>
+        <v>7310745</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,12 +1717,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1779,6 +1731,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1797,15 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119354067</v>
+        <v>119480782</v>
       </c>
       <c r="B13" t="n">
-        <v>79115</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,34 +1761,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>4745</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>799633</v>
+        <v>799654</v>
       </c>
       <c r="R13" t="n">
-        <v>7310576</v>
+        <v>7310992</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,12 +1815,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,50 +1847,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119354089</v>
+        <v>119480783</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>799564</v>
+        <v>799589</v>
       </c>
       <c r="R14" t="n">
-        <v>7310610</v>
+        <v>7310819</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,12 +1912,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,50 +1944,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119354115</v>
+        <v>119480784</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>799724</v>
+        <v>799640</v>
       </c>
       <c r="R15" t="n">
-        <v>7310667</v>
+        <v>7310636</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,12 +2009,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,15 +2041,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119354097</v>
+        <v>119480912</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,34 +2052,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>799745</v>
+        <v>799632</v>
       </c>
       <c r="R16" t="n">
-        <v>7310585</v>
+        <v>7311000</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,12 +2106,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2193,62 +2126,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119354110</v>
+        <v>119480913</v>
       </c>
       <c r="B17" t="n">
-        <v>97824</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>4745</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>799818</v>
+        <v>799615</v>
       </c>
       <c r="R17" t="n">
-        <v>7310580</v>
+        <v>7310828</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2275,12 +2203,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2295,27 +2223,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119354091</v>
+        <v>119354098</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,21 +2246,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2270,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>799686</v>
+        <v>799583</v>
       </c>
       <c r="R18" t="n">
-        <v>7310565</v>
+        <v>7310614</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2412,16 +2335,11 @@
         <v>119354099</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2511,50 +2429,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119354073</v>
+        <v>119480819</v>
       </c>
       <c r="B20" t="n">
-        <v>97928</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>799714</v>
+        <v>799622</v>
       </c>
       <c r="R20" t="n">
-        <v>7310644</v>
+        <v>7310864</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,12 +2494,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2595,6 +2508,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2613,15 +2527,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119354079</v>
+        <v>119354075</v>
       </c>
       <c r="B21" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2538,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2562,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>799732</v>
+        <v>799612</v>
       </c>
       <c r="R21" t="n">
-        <v>7310625</v>
+        <v>7310583</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,50 +2624,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119354095</v>
+        <v>119483565</v>
       </c>
       <c r="B22" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösön, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>799724</v>
+        <v>799548</v>
       </c>
       <c r="R22" t="n">
-        <v>7310534</v>
+        <v>7310853</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,12 +2697,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2805,62 +2717,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119354100</v>
+        <v>119480776</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>799701</v>
+        <v>799605</v>
       </c>
       <c r="R23" t="n">
-        <v>7310535</v>
+        <v>7310967</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,12 +2794,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2919,50 +2826,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119354092</v>
+        <v>119483561</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösön, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>799749</v>
+        <v>799602</v>
       </c>
       <c r="R24" t="n">
-        <v>7310559</v>
+        <v>7310887</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2989,12 +2891,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3009,12 +2911,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3024,12 +2926,7 @@
         <v>119354087</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3123,15 +3020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119354084</v>
+        <v>119354088</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,10 +3055,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>799775</v>
+        <v>799512</v>
       </c>
       <c r="R26" t="n">
-        <v>7310586</v>
+        <v>7310590</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,15 +3117,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119354085</v>
+        <v>119354089</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3265,10 +3152,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>799755</v>
+        <v>799564</v>
       </c>
       <c r="R27" t="n">
-        <v>7310585</v>
+        <v>7310610</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,37 +3214,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119354117</v>
+        <v>119354090</v>
       </c>
       <c r="B28" t="n">
-        <v>95202</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3249,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>799783</v>
+        <v>799583</v>
       </c>
       <c r="R28" t="n">
-        <v>7310537</v>
+        <v>7310620</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,50 +3311,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119354116</v>
+        <v>119480794</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>799722</v>
+        <v>799606</v>
       </c>
       <c r="R29" t="n">
-        <v>7310660</v>
+        <v>7310962</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3499,12 +3376,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3531,50 +3408,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119354105</v>
+        <v>119480795</v>
       </c>
       <c r="B30" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>799721</v>
+        <v>799573</v>
       </c>
       <c r="R30" t="n">
-        <v>7310524</v>
+        <v>7310958</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3601,12 +3473,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3633,50 +3505,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119354101</v>
+        <v>119480796</v>
       </c>
       <c r="B31" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>799575</v>
+        <v>799592</v>
       </c>
       <c r="R31" t="n">
-        <v>7310610</v>
+        <v>7310815</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3703,12 +3570,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3735,50 +3602,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119354094</v>
+        <v>119480797</v>
       </c>
       <c r="B32" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>799626</v>
+        <v>799531</v>
       </c>
       <c r="R32" t="n">
-        <v>7310570</v>
+        <v>7310646</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3805,12 +3667,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3837,50 +3699,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119354077</v>
+        <v>119480798</v>
       </c>
       <c r="B33" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>799693</v>
+        <v>799548</v>
       </c>
       <c r="R33" t="n">
-        <v>7310562</v>
+        <v>7310565</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3907,12 +3764,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3939,50 +3796,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119354071</v>
+        <v>119480801</v>
       </c>
       <c r="B34" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>799751</v>
+        <v>799535</v>
       </c>
       <c r="R34" t="n">
-        <v>7310584</v>
+        <v>7310561</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4009,12 +3861,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4041,50 +3893,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119354106</v>
+        <v>119480802</v>
       </c>
       <c r="B35" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>799802</v>
+        <v>799557</v>
       </c>
       <c r="R35" t="n">
-        <v>7310551</v>
+        <v>7310567</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4111,12 +3958,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4143,15 +3990,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119354086</v>
+        <v>119480915</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4179,14 +4021,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>799719</v>
+        <v>799602</v>
       </c>
       <c r="R36" t="n">
-        <v>7310642</v>
+        <v>7310818</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4213,12 +4055,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4233,62 +4075,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119354102</v>
+        <v>119480916</v>
       </c>
       <c r="B37" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>799623</v>
+        <v>799575</v>
       </c>
       <c r="R37" t="n">
-        <v>7310571</v>
+        <v>7310814</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4315,12 +4152,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4335,62 +4172,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119354096</v>
+        <v>119480918</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>799769</v>
+        <v>799566</v>
       </c>
       <c r="R38" t="n">
-        <v>7310585</v>
+        <v>7310572</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4417,12 +4249,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4437,62 +4269,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119354107</v>
+        <v>119480919</v>
       </c>
       <c r="B39" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>799801</v>
+        <v>799576</v>
       </c>
       <c r="R39" t="n">
-        <v>7310561</v>
+        <v>7310578</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4519,12 +4346,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4539,27 +4366,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119354083</v>
+        <v>119480920</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4587,11 +4409,11 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>799785</v>
+        <v>799655</v>
       </c>
       <c r="R40" t="n">
         <v>7310594</v>
@@ -4621,12 +4443,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4641,62 +4463,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Peter Lindqvist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119354074</v>
+        <v>119483590</v>
       </c>
       <c r="B41" t="n">
-        <v>97928</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösön, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>799576</v>
+        <v>799646</v>
       </c>
       <c r="R41" t="n">
-        <v>7310708</v>
+        <v>7310988</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4723,12 +4540,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4743,27 +4560,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119480794</v>
+        <v>119483592</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4791,14 +4603,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösön, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>799606</v>
+        <v>799627</v>
       </c>
       <c r="R42" t="n">
-        <v>7310962</v>
+        <v>7310949</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4845,62 +4657,57 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119480775</v>
+        <v>119483594</v>
       </c>
       <c r="B43" t="n">
-        <v>58138</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösön, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>799725</v>
+        <v>799557</v>
       </c>
       <c r="R43" t="n">
-        <v>7310578</v>
+        <v>7310866</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4947,62 +4754,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119480819</v>
+        <v>119483596</v>
       </c>
       <c r="B44" t="n">
-        <v>77910</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösön, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>799622</v>
+        <v>799508</v>
       </c>
       <c r="R44" t="n">
-        <v>7310864</v>
+        <v>7310659</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5043,69 +4845,63 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119480808</v>
+        <v>119483597</v>
       </c>
       <c r="B45" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösön, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>799610</v>
+        <v>799506</v>
       </c>
       <c r="R45" t="n">
-        <v>7310908</v>
+        <v>7310609</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5146,34 +4942,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119480801</v>
+        <v>119483599</v>
       </c>
       <c r="B46" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5201,14 +4991,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösön, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>799535</v>
+        <v>799522</v>
       </c>
       <c r="R46" t="n">
-        <v>7310561</v>
+        <v>7310592</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5243,6 +5033,11 @@
           <t>2024-09-01</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>minst 20m2</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5255,62 +5050,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119483590</v>
+        <v>119354074</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mjösön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>799646</v>
+        <v>799576</v>
       </c>
       <c r="R47" t="n">
-        <v>7310988</v>
+        <v>7310708</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5337,12 +5127,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5357,62 +5147,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119483576</v>
+        <v>119354067</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mjösön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>799723</v>
+        <v>799633</v>
       </c>
       <c r="R48" t="n">
-        <v>7310899</v>
+        <v>7310576</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5439,12 +5224,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5459,62 +5244,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119480817</v>
+        <v>119354095</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>799749</v>
+        <v>799724</v>
       </c>
       <c r="R49" t="n">
-        <v>7310870</v>
+        <v>7310534</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5541,12 +5321,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5573,50 +5353,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119480792</v>
+        <v>119354105</v>
       </c>
       <c r="B50" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>799728</v>
+        <v>799721</v>
       </c>
       <c r="R50" t="n">
-        <v>7310938</v>
+        <v>7310524</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5643,12 +5418,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5675,50 +5450,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119483570</v>
+        <v>119354106</v>
       </c>
       <c r="B51" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mjösön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>799768</v>
+        <v>799802</v>
       </c>
       <c r="R51" t="n">
-        <v>7310763</v>
+        <v>7310551</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5745,12 +5515,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5765,62 +5535,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119480789</v>
+        <v>119354107</v>
       </c>
       <c r="B52" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>799771</v>
+        <v>799801</v>
       </c>
       <c r="R52" t="n">
-        <v>7310662</v>
+        <v>7310561</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5847,12 +5612,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5879,50 +5644,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119483592</v>
+        <v>119354117</v>
       </c>
       <c r="B53" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mjösön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>799627</v>
+        <v>799783</v>
       </c>
       <c r="R53" t="n">
-        <v>7310949</v>
+        <v>7310537</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5949,12 +5709,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5969,62 +5729,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119480793</v>
+        <v>119354113</v>
       </c>
       <c r="B54" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>799694</v>
+        <v>799729</v>
       </c>
       <c r="R54" t="n">
-        <v>7311009</v>
+        <v>7310626</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6051,12 +5806,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6083,15 +5838,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119480815</v>
+        <v>119354114</v>
       </c>
       <c r="B55" t="n">
-        <v>90616</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6099,34 +5849,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3277</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>799561</v>
+        <v>799710</v>
       </c>
       <c r="R55" t="n">
-        <v>7310745</v>
+        <v>7310648</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6153,12 +5903,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6167,7 +5917,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6186,50 +5935,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119483574</v>
+        <v>119354115</v>
       </c>
       <c r="B56" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mjösön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>799734</v>
+        <v>799724</v>
       </c>
       <c r="R56" t="n">
-        <v>7310893</v>
+        <v>7310667</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6256,12 +6000,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6276,62 +6020,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119480914</v>
+        <v>119354116</v>
       </c>
       <c r="B57" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>799784</v>
+        <v>799722</v>
       </c>
       <c r="R57" t="n">
-        <v>7310596</v>
+        <v>7310660</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6358,12 +6097,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6378,27 +6117,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119480913</v>
+        <v>119480817</v>
       </c>
       <c r="B58" t="n">
-        <v>91463</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6406,21 +6140,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6430,10 +6164,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>799615</v>
+        <v>799749</v>
       </c>
       <c r="R58" t="n">
-        <v>7310828</v>
+        <v>7310870</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6480,62 +6214,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119480788</v>
+        <v>119354079</v>
       </c>
       <c r="B59" t="n">
-        <v>93935</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2387</v>
+        <v>4366</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>799531</v>
+        <v>799732</v>
       </c>
       <c r="R59" t="n">
-        <v>7310654</v>
+        <v>7310625</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6562,17 +6291,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>kolla upp</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6599,50 +6323,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119480802</v>
+        <v>119354072</v>
       </c>
       <c r="B60" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>799557</v>
+        <v>799710</v>
       </c>
       <c r="R60" t="n">
-        <v>7310567</v>
+        <v>7310658</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6669,12 +6388,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6701,15 +6420,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119480912</v>
+        <v>119480780</v>
       </c>
       <c r="B61" t="n">
-        <v>91463</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6741,10 +6455,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>799632</v>
+        <v>799719</v>
       </c>
       <c r="R61" t="n">
-        <v>7311000</v>
+        <v>7310708</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6791,12 +6505,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6806,12 +6520,7 @@
         <v>119480781</v>
       </c>
       <c r="B62" t="n">
-        <v>91463</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6905,50 +6614,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119480809</v>
+        <v>119354096</v>
       </c>
       <c r="B63" t="n">
-        <v>78608</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>799536</v>
+        <v>799769</v>
       </c>
       <c r="R63" t="n">
-        <v>7310553</v>
+        <v>7310585</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6975,12 +6679,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7007,15 +6711,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119480807</v>
+        <v>119354097</v>
       </c>
       <c r="B64" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7023,34 +6722,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>799805</v>
+        <v>799745</v>
       </c>
       <c r="R64" t="n">
-        <v>7310561</v>
+        <v>7310585</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7077,12 +6776,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7109,15 +6808,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119483568</v>
+        <v>119354100</v>
       </c>
       <c r="B65" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7125,34 +6819,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mjösön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>799765</v>
+        <v>799701</v>
       </c>
       <c r="R65" t="n">
-        <v>7310738</v>
+        <v>7310535</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7179,12 +6873,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7199,62 +6893,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119483578</v>
+        <v>119354077</v>
       </c>
       <c r="B66" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mjösön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>799705</v>
+        <v>799693</v>
       </c>
       <c r="R66" t="n">
-        <v>7310904</v>
+        <v>7310562</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7281,12 +6970,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7301,62 +6990,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119483596</v>
+        <v>119354071</v>
       </c>
       <c r="B67" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mjösön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>799508</v>
+        <v>799751</v>
       </c>
       <c r="R67" t="n">
-        <v>7310659</v>
+        <v>7310584</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7383,12 +7067,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7403,27 +7087,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119483561</v>
+        <v>119480775</v>
       </c>
       <c r="B68" t="n">
-        <v>58166</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7431,34 +7110,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mjösön, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>799602</v>
+        <v>799725</v>
       </c>
       <c r="R68" t="n">
-        <v>7310887</v>
+        <v>7310578</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7505,62 +7184,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119480784</v>
+        <v>119354110</v>
       </c>
       <c r="B69" t="n">
-        <v>91463</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4745</v>
+        <v>219790</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>799640</v>
+        <v>799818</v>
       </c>
       <c r="R69" t="n">
-        <v>7310636</v>
+        <v>7310580</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7587,12 +7261,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7619,15 +7293,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119480776</v>
+        <v>119480785</v>
       </c>
       <c r="B70" t="n">
-        <v>58166</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98186</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7635,21 +7304,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>208249</v>
+        <v>220250</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7659,10 +7328,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>799605</v>
+        <v>799809</v>
       </c>
       <c r="R70" t="n">
-        <v>7310967</v>
+        <v>7310563</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7721,15 +7390,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119480915</v>
+        <v>119354083</v>
       </c>
       <c r="B71" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7757,14 +7421,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>799602</v>
+        <v>799785</v>
       </c>
       <c r="R71" t="n">
-        <v>7310818</v>
+        <v>7310594</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7791,12 +7455,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7811,27 +7475,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119480798</v>
+        <v>119354084</v>
       </c>
       <c r="B72" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7859,14 +7518,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>799548</v>
+        <v>799775</v>
       </c>
       <c r="R72" t="n">
-        <v>7310565</v>
+        <v>7310586</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7893,12 +7552,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7925,15 +7584,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119480791</v>
+        <v>119354085</v>
       </c>
       <c r="B73" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7961,14 +7615,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>799747</v>
+        <v>799755</v>
       </c>
       <c r="R73" t="n">
-        <v>7310897</v>
+        <v>7310585</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7995,12 +7649,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8027,15 +7681,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119480804</v>
+        <v>119354086</v>
       </c>
       <c r="B74" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8063,14 +7712,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>799713</v>
+        <v>799719</v>
       </c>
       <c r="R74" t="n">
-        <v>7310569</v>
+        <v>7310642</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8097,12 +7746,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8129,15 +7778,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119480918</v>
+        <v>119354091</v>
       </c>
       <c r="B75" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8165,14 +7809,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>799566</v>
+        <v>799686</v>
       </c>
       <c r="R75" t="n">
-        <v>7310572</v>
+        <v>7310565</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8199,12 +7843,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8219,62 +7863,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119480783</v>
+        <v>119354092</v>
       </c>
       <c r="B76" t="n">
-        <v>91463</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>799589</v>
+        <v>799749</v>
       </c>
       <c r="R76" t="n">
-        <v>7310819</v>
+        <v>7310559</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8301,12 +7940,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8333,50 +7972,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119480785</v>
+        <v>119354093</v>
       </c>
       <c r="B77" t="n">
-        <v>97074</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220250</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>799809</v>
+        <v>799769</v>
       </c>
       <c r="R77" t="n">
-        <v>7310563</v>
+        <v>7310556</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8403,12 +8037,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8435,15 +8069,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119480797</v>
+        <v>119480789</v>
       </c>
       <c r="B78" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8475,10 +8104,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>799531</v>
+        <v>799771</v>
       </c>
       <c r="R78" t="n">
-        <v>7310646</v>
+        <v>7310662</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8537,15 +8166,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119480916</v>
+        <v>119480790</v>
       </c>
       <c r="B79" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8577,10 +8201,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>799575</v>
+        <v>799771</v>
       </c>
       <c r="R79" t="n">
-        <v>7310814</v>
+        <v>7310700</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8627,27 +8251,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119480920</v>
+        <v>119480791</v>
       </c>
       <c r="B80" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8679,10 +8298,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>799655</v>
+        <v>799747</v>
       </c>
       <c r="R80" t="n">
-        <v>7310594</v>
+        <v>7310897</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8729,49 +8348,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Peter Lindqvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119480814</v>
+        <v>119480792</v>
       </c>
       <c r="B81" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8781,10 +8395,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>799714</v>
+        <v>799728</v>
       </c>
       <c r="R81" t="n">
-        <v>7311012</v>
+        <v>7310938</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8843,15 +8457,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119483594</v>
+        <v>119480793</v>
       </c>
       <c r="B82" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8879,14 +8488,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Mjösön, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>799557</v>
+        <v>799694</v>
       </c>
       <c r="R82" t="n">
-        <v>7310866</v>
+        <v>7311009</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8933,27 +8542,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119480796</v>
+        <v>119480804</v>
       </c>
       <c r="B83" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8985,10 +8589,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>799592</v>
+        <v>799713</v>
       </c>
       <c r="R83" t="n">
-        <v>7310815</v>
+        <v>7310569</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9047,15 +8651,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119480790</v>
+        <v>119480807</v>
       </c>
       <c r="B84" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9087,10 +8686,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>799771</v>
+        <v>799805</v>
       </c>
       <c r="R84" t="n">
-        <v>7310700</v>
+        <v>7310561</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9149,15 +8748,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119480919</v>
+        <v>119480914</v>
       </c>
       <c r="B85" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9189,10 +8783,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>799576</v>
+        <v>799784</v>
       </c>
       <c r="R85" t="n">
-        <v>7310578</v>
+        <v>7310596</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9251,15 +8845,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119483597</v>
+        <v>119483566</v>
       </c>
       <c r="B86" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9291,10 +8880,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>799506</v>
+        <v>799765</v>
       </c>
       <c r="R86" t="n">
-        <v>7310609</v>
+        <v>7310625</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9353,15 +8942,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119483571</v>
+        <v>119483568</v>
       </c>
       <c r="B87" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9393,10 +8977,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>799762</v>
+        <v>799765</v>
       </c>
       <c r="R87" t="n">
-        <v>7310798</v>
+        <v>7310738</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9455,50 +9039,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119480782</v>
+        <v>119483570</v>
       </c>
       <c r="B88" t="n">
-        <v>91463</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösön, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>799654</v>
+        <v>799768</v>
       </c>
       <c r="R88" t="n">
-        <v>7310992</v>
+        <v>7310763</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9545,62 +9124,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119480780</v>
+        <v>119483571</v>
       </c>
       <c r="B89" t="n">
-        <v>91463</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösön, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>799719</v>
+        <v>799762</v>
       </c>
       <c r="R89" t="n">
-        <v>7310708</v>
+        <v>7310798</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9647,27 +9221,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119483589</v>
+        <v>119483574</v>
       </c>
       <c r="B90" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9699,10 +9268,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>799700</v>
+        <v>799734</v>
       </c>
       <c r="R90" t="n">
-        <v>7310952</v>
+        <v>7310893</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9761,15 +9330,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119480795</v>
+        <v>119483576</v>
       </c>
       <c r="B91" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9797,14 +9361,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösön, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>799573</v>
+        <v>799723</v>
       </c>
       <c r="R91" t="n">
-        <v>7310958</v>
+        <v>7310899</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9851,62 +9415,57 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119480813</v>
+        <v>119483578</v>
       </c>
       <c r="B92" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösön, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>799625</v>
+        <v>799705</v>
       </c>
       <c r="R92" t="n">
-        <v>7310588</v>
+        <v>7310904</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9947,34 +9506,28 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119483599</v>
+        <v>119483589</v>
       </c>
       <c r="B93" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10006,10 +9559,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>799522</v>
+        <v>799700</v>
       </c>
       <c r="R93" t="n">
-        <v>7310592</v>
+        <v>7310952</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10042,11 +9595,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>minst 20m2</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10073,15 +9621,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119483566</v>
+        <v>127742523</v>
       </c>
       <c r="B94" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10106,17 +9649,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Mjösön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>799765</v>
+        <v>799773</v>
       </c>
       <c r="R94" t="n">
-        <v>7310625</v>
+        <v>7310800</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10143,12 +9700,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-08-22</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10163,27 +9730,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119480778</v>
+        <v>119354073</v>
       </c>
       <c r="B95" t="n">
-        <v>97943</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10191,38 +9753,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>223621</v>
+        <v>221952</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Mjösjön, Nb</t>
+          <t>Mjösjön bdn, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>799760</v>
+        <v>799714</v>
       </c>
       <c r="R95" t="n">
-        <v>7310643</v>
+        <v>7310644</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10249,12 +9807,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10263,7 +9821,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10282,59 +9839,49 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127742523</v>
+        <v>119480778</v>
       </c>
       <c r="B96" t="n">
-        <v>98571</v>
+        <v>99155</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>223621</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Mjösjön bdn, Nb</t>
+          <t>Mjösjön, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>799773</v>
+        <v>799760</v>
       </c>
       <c r="R96" t="n">
-        <v>7310800</v>
+        <v>7310643</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10361,22 +9908,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>16:41</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>16:41</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10385,6 +9922,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31635-2024 artfynd.xlsx
+++ b/artfynd/A 31635-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354094</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354095</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480808</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480809</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354101</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354102</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354103</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354105</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354106</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354107</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354078</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1838,6 +1898,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480813</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1935,6 +2000,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354082</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2037,6 +2107,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480788</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2134,6 +2209,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354117</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2232,6 +2312,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480815</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2329,6 +2414,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354113</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2426,6 +2516,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354114</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2523,6 +2618,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354115</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2620,6 +2720,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354116</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2717,6 +2822,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480817</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2814,6 +2924,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354079</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2911,6 +3026,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354072</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3008,6 +3128,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480780</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3105,6 +3230,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480781</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3202,6 +3332,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480782</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3299,6 +3434,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480783</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3396,6 +3536,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480784</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3493,6 +3638,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480912</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3590,6 +3740,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480913</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3687,6 +3842,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354096</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3784,6 +3944,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354097</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3881,6 +4046,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354098</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3978,6 +4148,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354099</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4075,6 +4250,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354100</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4173,6 +4353,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480819</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4270,6 +4455,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354075</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4367,6 +4557,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354077</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4472,6 +4667,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483565</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4569,6 +4769,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354071</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4666,6 +4871,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480775</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4763,6 +4973,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480776</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4860,6 +5075,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483561</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4957,6 +5177,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354110</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5054,6 +5279,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480785</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5151,6 +5381,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354083</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5248,6 +5483,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354084</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5345,6 +5585,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354085</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5442,6 +5687,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354086</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5539,6 +5789,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354087</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5636,6 +5891,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354088</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5733,6 +5993,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354089</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5830,6 +6095,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354090</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5927,6 +6197,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354091</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6024,6 +6299,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354092</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6121,6 +6401,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354093</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6218,6 +6503,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480789</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6315,6 +6605,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480790</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6412,6 +6707,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480791</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6509,6 +6809,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480792</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6606,6 +6911,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480793</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6703,6 +7013,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480794</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6800,6 +7115,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480795</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6897,6 +7217,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480796</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6994,6 +7319,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480797</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7091,6 +7421,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480798</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7188,6 +7523,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480801</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7285,6 +7625,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480802</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7382,6 +7727,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480804</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7479,6 +7829,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480807</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7576,6 +7931,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480914</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7673,6 +8033,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480915</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7770,6 +8135,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480916</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7867,6 +8237,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480918</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7964,6 +8339,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480919</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8061,6 +8441,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480920</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8158,6 +8543,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483566</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8255,6 +8645,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483568</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8352,6 +8747,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483570</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8449,6 +8849,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483571</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8546,6 +8951,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483574</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8643,6 +9053,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483576</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8740,6 +9155,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483578</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8837,6 +9257,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483589</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8934,6 +9359,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483590</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9031,6 +9461,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483592</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9128,6 +9563,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483594</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9225,6 +9665,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483596</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9322,6 +9767,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483597</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9424,6 +9874,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483599</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9545,6 +10000,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127742523</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9642,6 +10102,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354073</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9739,6 +10204,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354074</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9841,6 +10311,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119480778</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9938,8 +10413,110 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119354067</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>